--- a/English/English Word.xlsx
+++ b/English/English Word.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\H0594499\开发文档\English\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView yWindow="15" windowWidth="19200" windowHeight="11865" tabRatio="413"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11865" tabRatio="413"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,14 +21,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
   <si>
     <r>
       <rPr>
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">agreement  </t>
     </r>
@@ -41,7 +46,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -67,7 +72,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">declare [dI'kleər]   </t>
     </r>
@@ -90,7 +95,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">finalize [ˈfaɪnəlaɪz]  </t>
     </r>
@@ -110,7 +115,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">get started </t>
     </r>
@@ -130,7 +135,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">host server  </t>
     </r>
@@ -150,7 +155,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">is made of  </t>
     </r>
@@ -168,7 +173,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>…</t>
     </r>
@@ -194,7 +199,7 @@
         <sz val="14"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">monitoring </t>
     </r>
@@ -214,7 +219,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">network  </t>
     </r>
@@ -237,7 +242,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">placeholder  </t>
     </r>
@@ -260,7 +265,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">reference ['refrəns]  </t>
     </r>
@@ -278,7 +283,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -298,7 +303,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">subscribe </t>
     </r>
@@ -330,7 +335,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">animations [ˌænɪˈmeɪʃ(ə)nz] </t>
     </r>
@@ -356,7 +361,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">domain [doʊˈmeɪn] </t>
     </r>
@@ -374,7 +379,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -397,7 +402,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">feature   </t>
     </r>
@@ -417,7 +422,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">generate [ˈdʒenəreɪt] </t>
     </r>
@@ -440,7 +445,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">introduce </t>
     </r>
@@ -449,7 +454,7 @@
         <sz val="14"/>
         <color rgb="FF0D0D0D"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>介绍</t>
     </r>
@@ -463,7 +468,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">mobile </t>
     </r>
@@ -489,7 +494,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">practice </t>
     </r>
@@ -512,7 +517,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">synchronize </t>
     </r>
@@ -544,7 +549,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">animal    </t>
     </r>
@@ -570,7 +575,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">dress </t>
     </r>
@@ -593,7 +598,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">framework </t>
     </r>
@@ -634,7 +639,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">platforms </t>
     </r>
@@ -657,7 +662,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">schedule </t>
     </r>
@@ -689,7 +694,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">across </t>
     </r>
@@ -715,7 +720,7 @@
         <sz val="14"/>
         <color rgb="FF333333"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">desktop [ˈdesktɑːp] </t>
     </r>
@@ -768,7 +773,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">schema  </t>
     </r>
@@ -786,7 +791,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -815,7 +820,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">application </t>
     </r>
@@ -833,7 +838,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -859,7 +864,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">develop </t>
     </r>
@@ -877,7 +882,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1510,9 +1515,6 @@
     <t>by sea 乘船</t>
   </si>
   <si>
-    <t>certain 某种 一定的</t>
-  </si>
-  <si>
     <t>Dependent [dɪˈpendənt] 依賴</t>
   </si>
   <si>
@@ -1621,284 +1623,912 @@
     <t>complete[kəmˈpliːt] 完整的</t>
   </si>
   <si>
+    <t>following 跟隨</t>
+  </si>
+  <si>
+    <t>in previous time [ˈpriːviəs] 在以前的時間</t>
+  </si>
+  <si>
+    <t>module 模塊 組件</t>
+  </si>
+  <si>
+    <t>phrase 短语</t>
+  </si>
+  <si>
+    <t>regress 倒退</t>
+  </si>
+  <si>
+    <t>sharp 锋利的</t>
+  </si>
+  <si>
+    <t>take 花費 耗費</t>
+  </si>
+  <si>
+    <t>auto  [ˈɔːtəʊ]自動的</t>
+  </si>
+  <si>
+    <t>beat [biːt]打败</t>
+  </si>
+  <si>
+    <t>coach 教练</t>
+  </si>
+  <si>
+    <t>filtering [ˈfɪltərɪŋ] 過濾</t>
+  </si>
+  <si>
+    <t>inform 通知</t>
+  </si>
+  <si>
+    <t xml:space="preserve">more visible  and clearly </t>
+  </si>
+  <si>
+    <t>powder 粉末</t>
+  </si>
+  <si>
+    <t>recovery 恢復</t>
+  </si>
+  <si>
+    <t>sight 情景 风景</t>
+  </si>
+  <si>
+    <t>translate into 轉化為</t>
+  </si>
+  <si>
+    <t>advanced [ədˈvɑːnst]先進的 高級的</t>
+  </si>
+  <si>
+    <t>Brazil [brəˈzɪl]巴西</t>
+  </si>
+  <si>
+    <t>collective [kəˈlektɪv]集体的</t>
+  </si>
+  <si>
+    <t>immediate [ɪˈmiːdiət] 立即的 直接的</t>
+  </si>
+  <si>
+    <t>Mandatory 是否強制性</t>
+  </si>
+  <si>
+    <t>programme 计划 规划</t>
+  </si>
+  <si>
+    <t>replay 答復</t>
+  </si>
+  <si>
+    <t>soil 土壤</t>
+  </si>
+  <si>
+    <t>troublesome 麻煩的</t>
+  </si>
+  <si>
+    <t>attitude [ˈætɪtjuːd]态度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">by myself  我自己來 </t>
+  </si>
+  <si>
+    <t>configuration 配置 結構</t>
+  </si>
+  <si>
+    <t>mutation 轉變 突變</t>
+  </si>
+  <si>
+    <t>percent 百分之..</t>
+  </si>
+  <si>
+    <t>recycle 回收</t>
+  </si>
+  <si>
+    <t>sow 播种</t>
+  </si>
+  <si>
+    <t>alone [əˈləʊn]独自的</t>
+  </si>
+  <si>
+    <t>be noted that  請注意</t>
+  </si>
+  <si>
+    <t>confirmation [ˌkɒnfəˈmeɪʃn] 確認證明</t>
+  </si>
+  <si>
+    <t>punish 处罚</t>
+  </si>
+  <si>
+    <t>recommend 建議</t>
+  </si>
+  <si>
+    <t>seed 种子</t>
+  </si>
+  <si>
+    <t>automatically[ˌɔːtəˈmætɪkli] 自動地 機械地</t>
+  </si>
+  <si>
+    <t>currently [ˈkʌrəntli]當前 一般</t>
+  </si>
+  <si>
+    <t>purpose 目的 意图</t>
+  </si>
+  <si>
+    <t>related 有關聯的</t>
+  </si>
+  <si>
+    <t>shade 树荫</t>
+  </si>
+  <si>
+    <t>actual [ˈæktʃuəl] 實際的</t>
+  </si>
+  <si>
+    <t>concerns [kənˈsɜːnz] 擔心</t>
+  </si>
+  <si>
+    <t>province 省</t>
+  </si>
+  <si>
+    <t>reversal 反轉</t>
+  </si>
+  <si>
+    <t>stranger 陌生人</t>
+  </si>
+  <si>
+    <t>complex [ˈkɒmpleks]複雜的</t>
+  </si>
+  <si>
+    <t>project 工程</t>
+  </si>
+  <si>
+    <t>supply 供应</t>
+  </si>
+  <si>
+    <t>corrective action  [kəˈrektɪv]改正措施</t>
+  </si>
+  <si>
+    <t>port 港口 码头</t>
+  </si>
+  <si>
+    <t>school leaver 毕业生</t>
+  </si>
+  <si>
+    <t>as my knowledge before 據我所知</t>
+  </si>
+  <si>
+    <t>cardinality [kɑːdɪ'nælɪtɪ] 基數</t>
+  </si>
+  <si>
+    <t>plenty of 充足 大量</t>
+  </si>
+  <si>
+    <t>spend on 在..花费</t>
+  </si>
+  <si>
+    <t>around 周圍</t>
+  </si>
+  <si>
+    <t>put up 贴广告</t>
+  </si>
+  <si>
+    <t>set up 建立</t>
+  </si>
+  <si>
+    <t>affect [əˈfekt] 影響</t>
+  </si>
+  <si>
+    <t>plant 工廠</t>
+  </si>
+  <si>
+    <t>spend..doing sth. 做..花费</t>
+  </si>
+  <si>
+    <t>poor 贫穷的 可怜的</t>
+  </si>
+  <si>
+    <t>sound lab 语言实验室</t>
+  </si>
+  <si>
+    <t>pro 专业的</t>
+  </si>
+  <si>
+    <t>screen 屏幕</t>
+  </si>
+  <si>
+    <t>pure 纯粹的</t>
+  </si>
+  <si>
+    <t>slash 斜線 嚴厲批評</t>
+  </si>
+  <si>
+    <t>particularly 異乎尋常的</t>
+  </si>
+  <si>
+    <t>suits 適合于</t>
+  </si>
+  <si>
+    <t>pending 未決定的</t>
+  </si>
+  <si>
+    <t>sports university 体育大学</t>
+  </si>
+  <si>
+    <t>precaution 預防措施</t>
+  </si>
+  <si>
+    <t>seriously 严肃的认真的</t>
+  </si>
+  <si>
+    <t>property 屬性</t>
+  </si>
+  <si>
+    <t>skill 本领 技术</t>
+  </si>
+  <si>
+    <t>spirit 精神</t>
+  </si>
+  <si>
+    <t>strategy 战略 策略</t>
+  </si>
+  <si>
+    <t>super 超級的</t>
+  </si>
+  <si>
+    <t>share 分享 公用</t>
+  </si>
+  <si>
+    <t>stamp 郵票 標誌</t>
+  </si>
+  <si>
+    <t>solution 解決辦法</t>
+  </si>
+  <si>
+    <t>symbols 符號 記號</t>
+  </si>
+  <si>
+    <r>
+      <t>almost [ˈɔ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ː</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>lməʊst]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>差不多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>幾乎</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>analysis [əˈnæləsɪs]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分解</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>communication[kəˌmjuːnɪˈkeɪʃn] 通讯</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>patterns 模式</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">certain </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>某种</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一定的</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">distributed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分布式的</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <t>deep 深度的 深刻的</t>
-  </si>
-  <si>
-    <t>following 跟隨</t>
-  </si>
-  <si>
-    <t>in previous time [ˈpriːviəs] 在以前的時間</t>
-  </si>
-  <si>
-    <t>module 模塊 組件</t>
-  </si>
-  <si>
-    <t>phrase 短语</t>
-  </si>
-  <si>
-    <t>regress 倒退</t>
-  </si>
-  <si>
-    <t>sharp 锋利的</t>
-  </si>
-  <si>
-    <t>take 花費 耗費</t>
-  </si>
-  <si>
-    <t>auto  [ˈɔːtəʊ]自動的</t>
-  </si>
-  <si>
-    <t>beat [biːt]打败</t>
-  </si>
-  <si>
-    <t>coach 教练</t>
-  </si>
-  <si>
-    <t>filtering [ˈfɪltərɪŋ] 過濾</t>
-  </si>
-  <si>
-    <t>inform 通知</t>
-  </si>
-  <si>
-    <t xml:space="preserve">more visible  and clearly </t>
-  </si>
-  <si>
-    <t>powder 粉末</t>
-  </si>
-  <si>
-    <t>recovery 恢復</t>
-  </si>
-  <si>
-    <t>sight 情景 风景</t>
-  </si>
-  <si>
-    <t>translate into 轉化為</t>
-  </si>
-  <si>
-    <t>advanced [ədˈvɑːnst]先進的 高級的</t>
-  </si>
-  <si>
-    <t>Brazil [brəˈzɪl]巴西</t>
-  </si>
-  <si>
-    <t>collective [kəˈlektɪv]集体的</t>
-  </si>
-  <si>
-    <t>immediate [ɪˈmiːdiət] 立即的 直接的</t>
-  </si>
-  <si>
-    <t>Mandatory 是否強制性</t>
-  </si>
-  <si>
-    <t>programme 计划 规划</t>
-  </si>
-  <si>
-    <t>replay 答復</t>
-  </si>
-  <si>
-    <t>soil 土壤</t>
-  </si>
-  <si>
-    <t>troublesome 麻煩的</t>
-  </si>
-  <si>
-    <t>attitude [ˈætɪtjuːd]态度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">by myself  我自己來 </t>
-  </si>
-  <si>
-    <t>configuration 配置 結構</t>
-  </si>
-  <si>
-    <t>mutation 轉變 突變</t>
-  </si>
-  <si>
-    <t>percent 百分之..</t>
-  </si>
-  <si>
-    <t>recycle 回收</t>
-  </si>
-  <si>
-    <t>sow 播种</t>
-  </si>
-  <si>
-    <t>alone [əˈləʊn]独自的</t>
-  </si>
-  <si>
-    <t>be noted that  請注意</t>
-  </si>
-  <si>
-    <t>confirmation [ˌkɒnfəˈmeɪʃn] 確認證明</t>
-  </si>
-  <si>
-    <t>punish 处罚</t>
-  </si>
-  <si>
-    <t>recommend 建議</t>
-  </si>
-  <si>
-    <t>seed 种子</t>
-  </si>
-  <si>
-    <t>automatically[ˌɔːtəˈmætɪkli] 自動地 機械地</t>
-  </si>
-  <si>
-    <t>currently [ˈkʌrəntli]當前 一般</t>
-  </si>
-  <si>
-    <t>purpose 目的 意图</t>
-  </si>
-  <si>
-    <t>related 有關聯的</t>
-  </si>
-  <si>
-    <t>shade 树荫</t>
-  </si>
-  <si>
-    <t>actual [ˈæktʃuəl] 實際的</t>
-  </si>
-  <si>
-    <t>concerns [kənˈsɜːnz] 擔心</t>
-  </si>
-  <si>
-    <t>province 省</t>
-  </si>
-  <si>
-    <t>reversal 反轉</t>
-  </si>
-  <si>
-    <t>stranger 陌生人</t>
-  </si>
-  <si>
-    <t>almost [ˈɔːlməʊst]差不多 幾乎</t>
-  </si>
-  <si>
-    <t>complex [ˈkɒmpleks]複雜的</t>
-  </si>
-  <si>
-    <t>project 工程</t>
-  </si>
-  <si>
-    <t>supply 供应</t>
-  </si>
-  <si>
-    <t>analysis [əˈnæləsɪs]分解</t>
-  </si>
-  <si>
-    <t>corrective action  [kəˈrektɪv]改正措施</t>
-  </si>
-  <si>
-    <t>port 港口 码头</t>
-  </si>
-  <si>
-    <t>school leaver 毕业生</t>
-  </si>
-  <si>
-    <t>as my knowledge before 據我所知</t>
-  </si>
-  <si>
-    <t>cardinality [kɑːdɪ'nælɪtɪ] 基數</t>
-  </si>
-  <si>
-    <t>plenty of 充足 大量</t>
-  </si>
-  <si>
-    <t>spend on 在..花费</t>
-  </si>
-  <si>
-    <t>around 周圍</t>
-  </si>
-  <si>
-    <t>put up 贴广告</t>
-  </si>
-  <si>
-    <t>set up 建立</t>
-  </si>
-  <si>
-    <t>affect [əˈfekt] 影響</t>
-  </si>
-  <si>
-    <t>plant 工廠</t>
-  </si>
-  <si>
-    <t>spend..doing sth. 做..花费</t>
-  </si>
-  <si>
-    <t>poor 贫穷的 可怜的</t>
-  </si>
-  <si>
-    <t>sound lab 语言实验室</t>
-  </si>
-  <si>
-    <t>pro 专业的</t>
-  </si>
-  <si>
-    <t>screen 屏幕</t>
-  </si>
-  <si>
-    <t>pure 纯粹的</t>
-  </si>
-  <si>
-    <t>slash 斜線 嚴厲批評</t>
-  </si>
-  <si>
-    <t>particularly 異乎尋常的</t>
-  </si>
-  <si>
-    <t>suits 適合于</t>
-  </si>
-  <si>
-    <t>pending 未決定的</t>
-  </si>
-  <si>
-    <t>sports university 体育大学</t>
-  </si>
-  <si>
-    <t>precaution 預防措施</t>
-  </si>
-  <si>
-    <t>seriously 严肃的认真的</t>
-  </si>
-  <si>
-    <t>property 屬性</t>
-  </si>
-  <si>
-    <t>skill 本领 技术</t>
-  </si>
-  <si>
-    <t>spirit 精神</t>
-  </si>
-  <si>
-    <t>strategy 战略 策略</t>
-  </si>
-  <si>
-    <t>super 超級的</t>
-  </si>
-  <si>
-    <t>share 分享 公用</t>
-  </si>
-  <si>
-    <t>stamp 郵票 標誌</t>
-  </si>
-  <si>
-    <t>solution 解決辦法</t>
-  </si>
-  <si>
-    <t>symbols 符號 記號</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>integration 集成</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">compatible </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>兼容的</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">infrastructure[ˈɪnfrəstrʌktʃə(r)] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>基础设施</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">determination </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>决心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>果断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测定</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">isolation </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>隔离</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>dynamic [daɪˈnæmɪk]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>动态的</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">unaware[ˌʌnəˈweə(r)] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不知道的</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cross cutting concerns </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>横切关注点</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>proxies['prɑksi] 代理</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">endpoint </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>末端</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">serialization </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>序列化</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>architecture [ˈ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ɑ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ː</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">kɪtektʃə(r)] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>架构</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>authentication [ɔ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ː</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ˌθentɪˈkeɪʃn] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>证明</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">virtual </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>虚拟的</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">embed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嵌入式</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">engine[ˈendʒɪn] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>引擎</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">middleware </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中间件</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">reduces </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>降低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>减少</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>boilerplate 样板文件</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">intellisense </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>智能感知</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cooperate [kəʊˈɒpəreɪt] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>合作配合</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">bundling </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>捆扎</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">minification </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>减小</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>缩小</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dependencies [dɪˈpendənsiz]  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>依赖</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">recursively </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>递归</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">determines </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>决定</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="32">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1910,175 +2540,32 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2115,7 +2602,7 @@
       <sz val="14"/>
       <color rgb="FF0D0D0D"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -2123,8 +2610,63 @@
       <name val="細明體"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2137,194 +2679,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2347,255 +2703,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2614,67 +2731,36 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="003399FF"/>
+      <color rgb="FF3399FF"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2959,19 +3045,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:W47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="44.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="43.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="31.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="44.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="33.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="33.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="21.875" style="1" customWidth="1"/>
@@ -2988,7 +3074,7 @@
     <col min="18" max="18" width="40.5" style="1" customWidth="1"/>
     <col min="19" max="19" width="27" style="1" customWidth="1"/>
     <col min="20" max="20" width="24.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="17.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="30.25" style="1" customWidth="1"/>
     <col min="22" max="22" width="24.75" style="1" customWidth="1"/>
     <col min="23" max="23" width="16.625" style="1" customWidth="1"/>
     <col min="24" max="24" width="17.5" style="1" customWidth="1"/>
@@ -2998,7 +3084,7 @@
     <col min="28" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3066,7 +3152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="18.75" spans="1:23">
+    <row r="2" spans="1:23" ht="20.25">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
@@ -3128,7 +3214,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" ht="20.25">
       <c r="A3" s="1" t="s">
         <v>42</v>
       </c>
@@ -3190,7 +3276,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" ht="20.25">
       <c r="A4" s="1" t="s">
         <v>62</v>
       </c>
@@ -3242,6 +3328,9 @@
       <c r="T4" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="U4" s="1" t="s">
+        <v>426</v>
+      </c>
       <c r="V4" s="2" t="s">
         <v>79</v>
       </c>
@@ -3249,7 +3338,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" ht="20.25">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
@@ -3423,7 +3512,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" ht="18.75" spans="1:23">
+    <row r="8" spans="1:23" ht="18.75">
       <c r="A8" s="2" t="s">
         <v>137</v>
       </c>
@@ -3471,6 +3560,9 @@
       </c>
       <c r="T8" s="2" t="s">
         <v>152</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>433</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>153</v>
@@ -3711,7 +3803,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:23">
       <c r="A14" s="2" t="s">
         <v>229</v>
       </c>
@@ -3749,7 +3841,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:23">
       <c r="A15" s="2" t="s">
         <v>241</v>
       </c>
@@ -3787,7 +3879,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:23">
       <c r="A16" s="2" t="s">
         <v>253</v>
       </c>
@@ -3901,7 +3993,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" ht="18.75">
       <c r="A19" s="2" t="s">
         <v>289</v>
       </c>
@@ -3909,480 +4001,588 @@
         <v>290</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="S20" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="S20" s="2" t="s">
+      <c r="T20" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="R21" s="2" t="s">
+      <c r="S21" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="S21" s="2" t="s">
+      <c r="T21" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="T21" s="2" t="s">
+    </row>
+    <row r="22" spans="1:20" ht="20.25">
+      <c r="A22" s="2" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="I22" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="S22" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="S22" s="2" t="s">
+    </row>
+    <row r="23" spans="1:20" ht="20.25">
+      <c r="A23" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="T22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="I23" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="S23" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="R23" s="2" t="s">
+      <c r="T23" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="S23" s="2" t="s">
+    </row>
+    <row r="24" spans="1:20" ht="18.75">
+      <c r="A24" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="T23" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="D24" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="M24" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="P24" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="R24" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="S24" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="R24" s="2" t="s">
+      <c r="T24" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="S24" s="2" t="s">
+    </row>
+    <row r="25" spans="1:20" ht="20.25">
+      <c r="A25" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="T24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="25" spans="1:19">
-      <c r="A25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="D25" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="R25" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="S25" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="R25" s="2" t="s">
+    </row>
+    <row r="26" spans="1:20" ht="18.75">
+      <c r="A26" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="S25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="26" spans="1:19">
-      <c r="A26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="D26" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="P26" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="R26" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="S26" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="R26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:20" ht="20.25">
+      <c r="A27" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="S26" s="2" t="s">
+      <c r="B27" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="27" ht="18.75" spans="1:19">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="P27" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="S27" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="R27" s="2" t="s">
+    </row>
+    <row r="28" spans="1:20" ht="18.75">
+      <c r="A28" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="S27" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="28" spans="1:19">
-      <c r="A28" s="2" t="s">
+      <c r="I28" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="R28" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="S28" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="R28" s="2" t="s">
+    </row>
+    <row r="29" spans="1:20" ht="20.25">
+      <c r="A29" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="S28" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="29" spans="1:19">
-      <c r="A29" s="2" t="s">
+      <c r="R29" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="S29" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:20" ht="18.75">
+      <c r="A30" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="R30" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="S30" s="2" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:20">
+      <c r="A31" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="S30" s="2" t="s">
+      <c r="S31" s="2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:20" ht="20.25">
+      <c r="A32" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="P32" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="S32" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="S31" s="2" t="s">
+    </row>
+    <row r="33" spans="1:19" ht="18.75">
+      <c r="A33" s="2" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="2" t="s">
+      <c r="C33" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="P33" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="S33" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="S32" s="2" t="s">
+    </row>
+    <row r="34" spans="1:19" ht="20.25">
+      <c r="A34" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="P34" s="2" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="33" spans="1:19">
-      <c r="A33" s="2" t="s">
+      <c r="S34" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="P33" s="2" t="s">
+    </row>
+    <row r="35" spans="1:19" ht="20.25">
+      <c r="A35" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="P35" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="S33" s="2" t="s">
+      <c r="S35" s="2" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="34" spans="16:19">
-      <c r="P34" s="2" t="s">
+    <row r="36" spans="1:19">
+      <c r="P36" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="S34" s="2" t="s">
+      <c r="S36" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="35" spans="16:19">
-      <c r="P35" s="2" t="s">
+    <row r="37" spans="1:19">
+      <c r="P37" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="S35" s="2" t="s">
+      <c r="S37" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="36" spans="16:19">
-      <c r="P36" s="2" t="s">
+    <row r="38" spans="1:19">
+      <c r="P38" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="S36" s="2" t="s">
+      <c r="S38" s="2" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="37" spans="16:19">
-      <c r="P37" s="2" t="s">
+    <row r="39" spans="1:19">
+      <c r="P39" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="S37" s="2" t="s">
+      <c r="S39" s="2" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="38" spans="16:19">
-      <c r="P38" s="2" t="s">
+    <row r="40" spans="1:19">
+      <c r="P40" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="S38" s="2" t="s">
+      <c r="S40" s="2" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="39" spans="16:19">
-      <c r="P39" s="2" t="s">
+    <row r="41" spans="1:19" ht="20.25">
+      <c r="P41" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="S41" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="S39" s="2" t="s">
+    </row>
+    <row r="42" spans="1:19" ht="20.25">
+      <c r="P42" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="S42" s="2" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="40" spans="16:19">
-      <c r="P40" s="1" t="s">
+    <row r="43" spans="1:19">
+      <c r="S43" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="S40" s="2" t="s">
+    </row>
+    <row r="44" spans="1:19">
+      <c r="S44" s="2" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="41" spans="19:19">
-      <c r="S41" s="2" t="s">
+    <row r="45" spans="1:19">
+      <c r="S45" s="2" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="42" spans="19:19">
-      <c r="S42" s="2" t="s">
+    <row r="46" spans="1:19">
+      <c r="S46" s="2" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="43" spans="19:19">
-      <c r="S43" s="2" t="s">
+    <row r="47" spans="1:19">
+      <c r="S47" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="44" spans="19:19">
-      <c r="S44" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="45" spans="19:19">
-      <c r="S45" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="46" spans="19:19">
-      <c r="S46" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="47" spans="19:19">
-      <c r="S47" s="1" t="s">
-        <v>416</v>
+    <row r="48" spans="1:19" ht="18.75">
+      <c r="S48" s="1" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="2"/>
+  <pixelatorList sheetStid="3"/>
+  <pixelatorList sheetStid="4"/>
+</pixelators>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<sheetInterline xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <interlineItem sheetStid="1" interlineOnOff="0" interlineColor="0"/>
+  <interlineItem sheetStid="2" interlineOnOff="0" interlineColor="0"/>
+  <interlineItem sheetStid="3" interlineOnOff="0" interlineColor="0"/>
+  <interlineItem sheetStid="4" interlineOnOff="0" interlineColor="0"/>
+</sheetInterline>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
+  <rangeList sheetStid="1" master=""/>
+  <rangeList sheetStid="2" master=""/>
+  <rangeList sheetStid="3" master=""/>
+</allowEditUser>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<mergeFile xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <listFile/>
+</mergeFile>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <settings xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookSettings>
     <isFilterShared>1</isFilterShared>
@@ -4392,40 +4592,12 @@
 </settings>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<mergeFile xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <listFile/>
-</mergeFile>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
-  <rangeList sheetStid="1" master=""/>
-  <rangeList sheetStid="2" master=""/>
-  <rangeList sheetStid="3" master=""/>
-</allowEditUser>
-</file>
-
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<sheetInterline xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <interlineItem sheetStid="1" interlineOnOff="0" interlineColor="0"/>
-  <interlineItem sheetStid="2" interlineOnOff="0" interlineColor="0"/>
-  <interlineItem sheetStid="3" interlineOnOff="0" interlineColor="0"/>
-  <interlineItem sheetStid="4" interlineOnOff="0" interlineColor="0"/>
-</sheetInterline>
-</file>
-
 <file path=customXml/item6.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="2"/>
-  <pixelatorList sheetStid="3"/>
-  <pixelatorList sheetStid="4"/>
-</pixelators>
+<comments xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A0048C-2381-489B-AA07-9611017176EA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
@@ -4434,6 +4606,33 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F8FC9E7-9E3E-4D00-BC07-C2C84DFACBCF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3875BF-13D6-4817-9B69-0B22B651B2C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F91F69C-6E8C-4246-BC25-297BFDC75D90}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
@@ -4442,35 +4641,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3875BF-13D6-4817-9B69-0B22B651B2C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F8FC9E7-9E3E-4D00-BC07-C2C84DFACBCF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps6.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A0048C-2381-489B-AA07-9611017176EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
